--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1051"/>
+  <dimension ref="A1:H1052"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27722,6 +27722,32 @@
         <v>57425</v>
       </c>
     </row>
+    <row r="1052" spans="1:8">
+      <c r="A1052" s="1">
+        <v>1050</v>
+      </c>
+      <c r="B1052" s="2">
+        <v>46083</v>
+      </c>
+      <c r="C1052">
+        <v>3226</v>
+      </c>
+      <c r="D1052">
+        <v>13230</v>
+      </c>
+      <c r="E1052">
+        <v>1934</v>
+      </c>
+      <c r="F1052">
+        <v>17335</v>
+      </c>
+      <c r="G1052">
+        <v>3354</v>
+      </c>
+      <c r="H1052">
+        <v>57200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1052"/>
+  <dimension ref="A1:H1053"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27748,6 +27748,32 @@
         <v>57200</v>
       </c>
     </row>
+    <row r="1053" spans="1:8">
+      <c r="A1053" s="1">
+        <v>1051</v>
+      </c>
+      <c r="B1053" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C1053">
+        <v>3269</v>
+      </c>
+      <c r="D1053">
+        <v>12820</v>
+      </c>
+      <c r="E1053">
+        <v>1902</v>
+      </c>
+      <c r="F1053">
+        <v>17000</v>
+      </c>
+      <c r="G1053">
+        <v>3287</v>
+      </c>
+      <c r="H1053">
+        <v>49700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1053"/>
+  <dimension ref="A1:H1054"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27774,6 +27774,32 @@
         <v>49700</v>
       </c>
     </row>
+    <row r="1054" spans="1:8">
+      <c r="A1054" s="1">
+        <v>1052</v>
+      </c>
+      <c r="B1054" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C1054">
+        <v>3378</v>
+      </c>
+      <c r="D1054">
+        <v>12960</v>
+      </c>
+      <c r="E1054">
+        <v>1903</v>
+      </c>
+      <c r="F1054">
+        <v>17395</v>
+      </c>
+      <c r="G1054">
+        <v>3282</v>
+      </c>
+      <c r="H1054">
+        <v>51425</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1054"/>
+  <dimension ref="A1:H1055"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27800,6 +27800,32 @@
         <v>51425</v>
       </c>
     </row>
+    <row r="1055" spans="1:8">
+      <c r="A1055" s="1">
+        <v>1053</v>
+      </c>
+      <c r="B1055" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C1055">
+        <v>3298.5</v>
+      </c>
+      <c r="D1055">
+        <v>12841</v>
+      </c>
+      <c r="E1055">
+        <v>1904.5</v>
+      </c>
+      <c r="F1055">
+        <v>17110</v>
+      </c>
+      <c r="G1055">
+        <v>3267</v>
+      </c>
+      <c r="H1055">
+        <v>49850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1055"/>
+  <dimension ref="A1:H1056"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27826,6 +27826,32 @@
         <v>49850</v>
       </c>
     </row>
+    <row r="1056" spans="1:8">
+      <c r="A1056" s="1">
+        <v>1054</v>
+      </c>
+      <c r="B1056" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C1056">
+        <v>3385</v>
+      </c>
+      <c r="D1056">
+        <v>12808</v>
+      </c>
+      <c r="E1056">
+        <v>1900.5</v>
+      </c>
+      <c r="F1056">
+        <v>17200</v>
+      </c>
+      <c r="G1056">
+        <v>3238</v>
+      </c>
+      <c r="H1056">
+        <v>50400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1056"/>
+  <dimension ref="A1:H1057"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27852,6 +27852,32 @@
         <v>50400</v>
       </c>
     </row>
+    <row r="1057" spans="1:8">
+      <c r="A1057" s="1">
+        <v>1055</v>
+      </c>
+      <c r="B1057" s="2">
+        <v>46090</v>
+      </c>
+      <c r="C1057">
+        <v>3406.5</v>
+      </c>
+      <c r="D1057">
+        <v>12750.5</v>
+      </c>
+      <c r="E1057">
+        <v>1894.5</v>
+      </c>
+      <c r="F1057">
+        <v>17290</v>
+      </c>
+      <c r="G1057">
+        <v>3320</v>
+      </c>
+      <c r="H1057">
+        <v>48275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1057"/>
+  <dimension ref="A1:H1058"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27878,6 +27878,32 @@
         <v>48275</v>
       </c>
     </row>
+    <row r="1058" spans="1:8">
+      <c r="A1058" s="1">
+        <v>1056</v>
+      </c>
+      <c r="B1058" s="2">
+        <v>46091</v>
+      </c>
+      <c r="C1058">
+        <v>3402.5</v>
+      </c>
+      <c r="D1058">
+        <v>12920.5</v>
+      </c>
+      <c r="E1058">
+        <v>1895</v>
+      </c>
+      <c r="F1058">
+        <v>17310</v>
+      </c>
+      <c r="G1058">
+        <v>3334</v>
+      </c>
+      <c r="H1058">
+        <v>50005</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1058"/>
+  <dimension ref="A1:H1059"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27904,6 +27904,32 @@
         <v>50005</v>
       </c>
     </row>
+    <row r="1059" spans="1:8">
+      <c r="A1059" s="1">
+        <v>1057</v>
+      </c>
+      <c r="B1059" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C1059">
+        <v>3467</v>
+      </c>
+      <c r="D1059">
+        <v>12850.5</v>
+      </c>
+      <c r="E1059">
+        <v>1886</v>
+      </c>
+      <c r="F1059">
+        <v>17220</v>
+      </c>
+      <c r="G1059">
+        <v>3268</v>
+      </c>
+      <c r="H1059">
+        <v>49900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1059"/>
+  <dimension ref="A1:H1060"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27930,6 +27930,32 @@
         <v>49900</v>
       </c>
     </row>
+    <row r="1060" spans="1:8">
+      <c r="A1060" s="1">
+        <v>1058</v>
+      </c>
+      <c r="B1060" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C1060">
+        <v>3516.5</v>
+      </c>
+      <c r="D1060">
+        <v>12896.5</v>
+      </c>
+      <c r="E1060">
+        <v>1894</v>
+      </c>
+      <c r="F1060">
+        <v>17500</v>
+      </c>
+      <c r="G1060">
+        <v>3264</v>
+      </c>
+      <c r="H1060">
+        <v>49725</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1060"/>
+  <dimension ref="A1:H1061"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27956,6 +27956,32 @@
         <v>49725</v>
       </c>
     </row>
+    <row r="1061" spans="1:8">
+      <c r="A1061" s="1">
+        <v>1059</v>
+      </c>
+      <c r="B1061" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C1061">
+        <v>3520</v>
+      </c>
+      <c r="D1061">
+        <v>12758</v>
+      </c>
+      <c r="E1061">
+        <v>1880</v>
+      </c>
+      <c r="F1061">
+        <v>17340</v>
+      </c>
+      <c r="G1061">
+        <v>3270</v>
+      </c>
+      <c r="H1061">
+        <v>47950</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1061"/>
+  <dimension ref="A1:H1062"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -27982,6 +27982,32 @@
         <v>47950</v>
       </c>
     </row>
+    <row r="1062" spans="1:8">
+      <c r="A1062" s="1">
+        <v>1060</v>
+      </c>
+      <c r="B1062" s="2">
+        <v>46097</v>
+      </c>
+      <c r="C1062">
+        <v>3440</v>
+      </c>
+      <c r="D1062">
+        <v>12759.5</v>
+      </c>
+      <c r="E1062">
+        <v>1854</v>
+      </c>
+      <c r="F1062">
+        <v>17120</v>
+      </c>
+      <c r="G1062">
+        <v>3240</v>
+      </c>
+      <c r="H1062">
+        <v>48000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1062"/>
+  <dimension ref="A1:H1063"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28008,6 +28008,32 @@
         <v>48000</v>
       </c>
     </row>
+    <row r="1063" spans="1:8">
+      <c r="A1063" s="1">
+        <v>1061</v>
+      </c>
+      <c r="B1063" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C1063">
+        <v>3426</v>
+      </c>
+      <c r="D1063">
+        <v>12677</v>
+      </c>
+      <c r="E1063">
+        <v>1886</v>
+      </c>
+      <c r="F1063">
+        <v>17200</v>
+      </c>
+      <c r="G1063">
+        <v>3189</v>
+      </c>
+      <c r="H1063">
+        <v>46805</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1063"/>
+  <dimension ref="A1:H1064"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28034,6 +28034,32 @@
         <v>46805</v>
       </c>
     </row>
+    <row r="1064" spans="1:8">
+      <c r="A1064" s="1">
+        <v>1062</v>
+      </c>
+      <c r="B1064" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C1064">
+        <v>3400</v>
+      </c>
+      <c r="D1064">
+        <v>12503</v>
+      </c>
+      <c r="E1064">
+        <v>1880</v>
+      </c>
+      <c r="F1064">
+        <v>16990</v>
+      </c>
+      <c r="G1064">
+        <v>3124</v>
+      </c>
+      <c r="H1064">
+        <v>46295</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1064"/>
+  <dimension ref="A1:H1065"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28060,6 +28060,32 @@
         <v>46295</v>
       </c>
     </row>
+    <row r="1065" spans="1:8">
+      <c r="A1065" s="1">
+        <v>1063</v>
+      </c>
+      <c r="B1065" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C1065">
+        <v>3200</v>
+      </c>
+      <c r="D1065">
+        <v>11826</v>
+      </c>
+      <c r="E1065">
+        <v>1828</v>
+      </c>
+      <c r="F1065">
+        <v>16290</v>
+      </c>
+      <c r="G1065">
+        <v>3010</v>
+      </c>
+      <c r="H1065">
+        <v>41700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1065"/>
+  <dimension ref="A1:H1066"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28086,6 +28086,32 @@
         <v>41700</v>
       </c>
     </row>
+    <row r="1066" spans="1:8">
+      <c r="A1066" s="1">
+        <v>1064</v>
+      </c>
+      <c r="B1066" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C1066">
+        <v>3329</v>
+      </c>
+      <c r="D1066">
+        <v>12021.5</v>
+      </c>
+      <c r="E1066">
+        <v>1861</v>
+      </c>
+      <c r="F1066">
+        <v>16770</v>
+      </c>
+      <c r="G1066">
+        <v>3065.5</v>
+      </c>
+      <c r="H1066">
+        <v>43700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1066"/>
+  <dimension ref="A1:H1067"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28112,6 +28112,32 @@
         <v>43700</v>
       </c>
     </row>
+    <row r="1067" spans="1:8">
+      <c r="A1067" s="1">
+        <v>1065</v>
+      </c>
+      <c r="B1067" s="2">
+        <v>46104</v>
+      </c>
+      <c r="C1067">
+        <v>3251.5</v>
+      </c>
+      <c r="D1067">
+        <v>11891</v>
+      </c>
+      <c r="E1067">
+        <v>1861</v>
+      </c>
+      <c r="F1067">
+        <v>16900</v>
+      </c>
+      <c r="G1067">
+        <v>3040</v>
+      </c>
+      <c r="H1067">
+        <v>43425</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1067"/>
+  <dimension ref="A1:H1068"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28138,6 +28138,32 @@
         <v>43425</v>
       </c>
     </row>
+    <row r="1068" spans="1:8">
+      <c r="A1068" s="1">
+        <v>1066</v>
+      </c>
+      <c r="B1068" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C1068">
+        <v>3242.5</v>
+      </c>
+      <c r="D1068">
+        <v>11878.5</v>
+      </c>
+      <c r="E1068">
+        <v>1850</v>
+      </c>
+      <c r="F1068">
+        <v>16830</v>
+      </c>
+      <c r="G1068">
+        <v>3037</v>
+      </c>
+      <c r="H1068">
+        <v>43750</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1068"/>
+  <dimension ref="A1:H1069"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28164,6 +28164,32 @@
         <v>43750</v>
       </c>
     </row>
+    <row r="1069" spans="1:8">
+      <c r="A1069" s="1">
+        <v>1067</v>
+      </c>
+      <c r="B1069" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C1069">
+        <v>3294.5</v>
+      </c>
+      <c r="D1069">
+        <v>12135</v>
+      </c>
+      <c r="E1069">
+        <v>1882.5</v>
+      </c>
+      <c r="F1069">
+        <v>17320</v>
+      </c>
+      <c r="G1069">
+        <v>3047</v>
+      </c>
+      <c r="H1069">
+        <v>45525</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1069"/>
+  <dimension ref="A1:H1070"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28190,6 +28190,32 @@
         <v>45525</v>
       </c>
     </row>
+    <row r="1070" spans="1:8">
+      <c r="A1070" s="1">
+        <v>1068</v>
+      </c>
+      <c r="B1070" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C1070">
+        <v>3332</v>
+      </c>
+      <c r="D1070">
+        <v>12108</v>
+      </c>
+      <c r="E1070">
+        <v>1850</v>
+      </c>
+      <c r="F1070">
+        <v>17020</v>
+      </c>
+      <c r="G1070">
+        <v>3077</v>
+      </c>
+      <c r="H1070">
+        <v>44400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1070"/>
+  <dimension ref="A1:H1071"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28216,6 +28216,32 @@
         <v>44400</v>
       </c>
     </row>
+    <row r="1071" spans="1:8">
+      <c r="A1071" s="1">
+        <v>1069</v>
+      </c>
+      <c r="B1071" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C1071">
+        <v>3292</v>
+      </c>
+      <c r="D1071">
+        <v>12046</v>
+      </c>
+      <c r="E1071">
+        <v>1855</v>
+      </c>
+      <c r="F1071">
+        <v>17010</v>
+      </c>
+      <c r="G1071">
+        <v>3075</v>
+      </c>
+      <c r="H1071">
+        <v>44850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1071"/>
+  <dimension ref="A1:H1072"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28242,6 +28242,32 @@
         <v>44850</v>
       </c>
     </row>
+    <row r="1072" spans="1:8">
+      <c r="A1072" s="1">
+        <v>1070</v>
+      </c>
+      <c r="B1072" s="2">
+        <v>46111</v>
+      </c>
+      <c r="C1072">
+        <v>3482</v>
+      </c>
+      <c r="D1072">
+        <v>12137</v>
+      </c>
+      <c r="E1072">
+        <v>1873</v>
+      </c>
+      <c r="F1072">
+        <v>17040</v>
+      </c>
+      <c r="G1072">
+        <v>3161</v>
+      </c>
+      <c r="H1072">
+        <v>46850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1072"/>
+  <dimension ref="A1:H1073"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28268,6 +28268,32 @@
         <v>46850</v>
       </c>
     </row>
+    <row r="1073" spans="1:8">
+      <c r="A1073" s="1">
+        <v>1071</v>
+      </c>
+      <c r="B1073" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C1073">
+        <v>3585</v>
+      </c>
+      <c r="D1073">
+        <v>12160</v>
+      </c>
+      <c r="E1073">
+        <v>1881</v>
+      </c>
+      <c r="F1073">
+        <v>16860</v>
+      </c>
+      <c r="G1073">
+        <v>3184.5</v>
+      </c>
+      <c r="H1073">
+        <v>45610</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1073"/>
+  <dimension ref="A1:H1074"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28294,6 +28294,32 @@
         <v>45610</v>
       </c>
     </row>
+    <row r="1074" spans="1:8">
+      <c r="A1074" s="1">
+        <v>1072</v>
+      </c>
+      <c r="B1074" s="2">
+        <v>46113</v>
+      </c>
+      <c r="C1074">
+        <v>3583.5</v>
+      </c>
+      <c r="D1074">
+        <v>12270</v>
+      </c>
+      <c r="E1074">
+        <v>1892</v>
+      </c>
+      <c r="F1074">
+        <v>17065</v>
+      </c>
+      <c r="G1074">
+        <v>3237</v>
+      </c>
+      <c r="H1074">
+        <v>47795</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1074"/>
+  <dimension ref="A1:H1075"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28320,6 +28320,32 @@
         <v>47795</v>
       </c>
     </row>
+    <row r="1075" spans="1:8">
+      <c r="A1075" s="1">
+        <v>1073</v>
+      </c>
+      <c r="B1075" s="2">
+        <v>46114</v>
+      </c>
+      <c r="C1075">
+        <v>3505</v>
+      </c>
+      <c r="D1075">
+        <v>12147</v>
+      </c>
+      <c r="E1075">
+        <v>1893</v>
+      </c>
+      <c r="F1075">
+        <v>16900</v>
+      </c>
+      <c r="G1075">
+        <v>3235</v>
+      </c>
+      <c r="H1075">
+        <v>45250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1075"/>
+  <dimension ref="A1:H1076"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28346,6 +28346,32 @@
         <v>45250</v>
       </c>
     </row>
+    <row r="1076" spans="1:8">
+      <c r="A1076" s="1">
+        <v>1074</v>
+      </c>
+      <c r="B1076" s="2">
+        <v>46119</v>
+      </c>
+      <c r="C1076">
+        <v>3600</v>
+      </c>
+      <c r="D1076">
+        <v>12252</v>
+      </c>
+      <c r="E1076">
+        <v>1903</v>
+      </c>
+      <c r="F1076">
+        <v>16840</v>
+      </c>
+      <c r="G1076">
+        <v>3320</v>
+      </c>
+      <c r="H1076">
+        <v>46025</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1076"/>
+  <dimension ref="A1:H1077"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28372,6 +28372,32 @@
         <v>46025</v>
       </c>
     </row>
+    <row r="1077" spans="1:8">
+      <c r="A1077" s="1">
+        <v>1075</v>
+      </c>
+      <c r="B1077" s="2">
+        <v>46120</v>
+      </c>
+      <c r="C1077">
+        <v>3520</v>
+      </c>
+      <c r="D1077">
+        <v>12552</v>
+      </c>
+      <c r="E1077">
+        <v>1920</v>
+      </c>
+      <c r="F1077">
+        <v>17200</v>
+      </c>
+      <c r="G1077">
+        <v>3295</v>
+      </c>
+      <c r="H1077">
+        <v>47895</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1077"/>
+  <dimension ref="A1:H1078"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28398,6 +28398,32 @@
         <v>47895</v>
       </c>
     </row>
+    <row r="1078" spans="1:8">
+      <c r="A1078" s="1">
+        <v>1076</v>
+      </c>
+      <c r="B1078" s="2">
+        <v>46121</v>
+      </c>
+      <c r="C1078">
+        <v>3494.5</v>
+      </c>
+      <c r="D1078">
+        <v>12455</v>
+      </c>
+      <c r="E1078">
+        <v>1893.5</v>
+      </c>
+      <c r="F1078">
+        <v>17025</v>
+      </c>
+      <c r="G1078">
+        <v>3256</v>
+      </c>
+      <c r="H1078">
+        <v>46725</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1078"/>
+  <dimension ref="A1:H1079"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28424,6 +28424,32 @@
         <v>46725</v>
       </c>
     </row>
+    <row r="1079" spans="1:8">
+      <c r="A1079" s="1">
+        <v>1077</v>
+      </c>
+      <c r="B1079" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C1079">
+        <v>3526</v>
+      </c>
+      <c r="D1079">
+        <v>12660.5</v>
+      </c>
+      <c r="E1079">
+        <v>1882</v>
+      </c>
+      <c r="F1079">
+        <v>17070</v>
+      </c>
+      <c r="G1079">
+        <v>3297</v>
+      </c>
+      <c r="H1079">
+        <v>47975</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1079"/>
+  <dimension ref="A1:H1080"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28450,6 +28450,32 @@
         <v>47975</v>
       </c>
     </row>
+    <row r="1080" spans="1:8">
+      <c r="A1080" s="1">
+        <v>1078</v>
+      </c>
+      <c r="B1080" s="2">
+        <v>46125</v>
+      </c>
+      <c r="C1080">
+        <v>3665.5</v>
+      </c>
+      <c r="D1080">
+        <v>12820.5</v>
+      </c>
+      <c r="E1080">
+        <v>1885</v>
+      </c>
+      <c r="F1080">
+        <v>17490</v>
+      </c>
+      <c r="G1080">
+        <v>3304.5</v>
+      </c>
+      <c r="H1080">
+        <v>47705</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1080"/>
+  <dimension ref="A1:H1081"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28476,6 +28476,32 @@
         <v>47705</v>
       </c>
     </row>
+    <row r="1081" spans="1:8">
+      <c r="A1081" s="1">
+        <v>1079</v>
+      </c>
+      <c r="B1081" s="2">
+        <v>46126</v>
+      </c>
+      <c r="C1081">
+        <v>3625</v>
+      </c>
+      <c r="D1081">
+        <v>13095</v>
+      </c>
+      <c r="E1081">
+        <v>1889</v>
+      </c>
+      <c r="F1081">
+        <v>17750</v>
+      </c>
+      <c r="G1081">
+        <v>3300</v>
+      </c>
+      <c r="H1081">
+        <v>49500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1081"/>
+  <dimension ref="A1:H1082"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28502,6 +28502,32 @@
         <v>49500</v>
       </c>
     </row>
+    <row r="1082" spans="1:8">
+      <c r="A1082" s="1">
+        <v>1080</v>
+      </c>
+      <c r="B1082" s="2">
+        <v>46127</v>
+      </c>
+      <c r="C1082">
+        <v>3581</v>
+      </c>
+      <c r="D1082">
+        <v>13155</v>
+      </c>
+      <c r="E1082">
+        <v>1925</v>
+      </c>
+      <c r="F1082">
+        <v>18075</v>
+      </c>
+      <c r="G1082">
+        <v>3362</v>
+      </c>
+      <c r="H1082">
+        <v>49955</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1082"/>
+  <dimension ref="A1:H1083"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28528,6 +28528,32 @@
         <v>49955</v>
       </c>
     </row>
+    <row r="1083" spans="1:8">
+      <c r="A1083" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B1083" s="2">
+        <v>46128</v>
+      </c>
+      <c r="C1083">
+        <v>3678.5</v>
+      </c>
+      <c r="D1083">
+        <v>13180</v>
+      </c>
+      <c r="E1083">
+        <v>1917.5</v>
+      </c>
+      <c r="F1083">
+        <v>18070</v>
+      </c>
+      <c r="G1083">
+        <v>3415</v>
+      </c>
+      <c r="H1083">
+        <v>49700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1083"/>
+  <dimension ref="A1:H1084"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28554,6 +28554,32 @@
         <v>49700</v>
       </c>
     </row>
+    <row r="1084" spans="1:8">
+      <c r="A1084" s="1">
+        <v>1082</v>
+      </c>
+      <c r="B1084" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C1084">
+        <v>3660</v>
+      </c>
+      <c r="D1084">
+        <v>13149</v>
+      </c>
+      <c r="E1084">
+        <v>1949</v>
+      </c>
+      <c r="F1084">
+        <v>18380</v>
+      </c>
+      <c r="G1084">
+        <v>3439</v>
+      </c>
+      <c r="H1084">
+        <v>49675</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1084"/>
+  <dimension ref="A1:H1085"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28580,6 +28580,32 @@
         <v>49675</v>
       </c>
     </row>
+    <row r="1085" spans="1:8">
+      <c r="A1085" s="1">
+        <v>1083</v>
+      </c>
+      <c r="B1085" s="2">
+        <v>46132</v>
+      </c>
+      <c r="C1085">
+        <v>3590</v>
+      </c>
+      <c r="D1085">
+        <v>13163</v>
+      </c>
+      <c r="E1085">
+        <v>1932.5</v>
+      </c>
+      <c r="F1085">
+        <v>17980</v>
+      </c>
+      <c r="G1085">
+        <v>3430</v>
+      </c>
+      <c r="H1085">
+        <v>50250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1085"/>
+  <dimension ref="A1:H1086"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28606,6 +28606,32 @@
         <v>50250</v>
       </c>
     </row>
+    <row r="1086" spans="1:8">
+      <c r="A1086" s="1">
+        <v>1084</v>
+      </c>
+      <c r="B1086" s="2">
+        <v>46133</v>
+      </c>
+      <c r="C1086">
+        <v>3613</v>
+      </c>
+      <c r="D1086">
+        <v>13200.5</v>
+      </c>
+      <c r="E1086">
+        <v>1982</v>
+      </c>
+      <c r="F1086">
+        <v>18120</v>
+      </c>
+      <c r="G1086">
+        <v>3438</v>
+      </c>
+      <c r="H1086">
+        <v>50850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1086"/>
+  <dimension ref="A1:H1087"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28632,6 +28632,32 @@
         <v>50850</v>
       </c>
     </row>
+    <row r="1087" spans="1:8">
+      <c r="A1087" s="1">
+        <v>1085</v>
+      </c>
+      <c r="B1087" s="2">
+        <v>46134</v>
+      </c>
+      <c r="C1087">
+        <v>3652</v>
+      </c>
+      <c r="D1087">
+        <v>13198</v>
+      </c>
+      <c r="E1087">
+        <v>1927</v>
+      </c>
+      <c r="F1087">
+        <v>18180</v>
+      </c>
+      <c r="G1087">
+        <v>3468</v>
+      </c>
+      <c r="H1087">
+        <v>50125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1087"/>
+  <dimension ref="A1:H1088"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28658,6 +28658,32 @@
         <v>50125</v>
       </c>
     </row>
+    <row r="1088" spans="1:8">
+      <c r="A1088" s="1">
+        <v>1086</v>
+      </c>
+      <c r="B1088" s="2">
+        <v>46135</v>
+      </c>
+      <c r="C1088">
+        <v>3642</v>
+      </c>
+      <c r="D1088">
+        <v>13190</v>
+      </c>
+      <c r="E1088">
+        <v>1940.5</v>
+      </c>
+      <c r="F1088">
+        <v>18425</v>
+      </c>
+      <c r="G1088">
+        <v>3446</v>
+      </c>
+      <c r="H1088">
+        <v>50250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1088"/>
+  <dimension ref="A1:H1089"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28684,6 +28684,32 @@
         <v>50250</v>
       </c>
     </row>
+    <row r="1089" spans="1:8">
+      <c r="A1089" s="1">
+        <v>1087</v>
+      </c>
+      <c r="B1089" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C1089">
+        <v>3685</v>
+      </c>
+      <c r="D1089">
+        <v>13230</v>
+      </c>
+      <c r="E1089">
+        <v>1954</v>
+      </c>
+      <c r="F1089">
+        <v>18625</v>
+      </c>
+      <c r="G1089">
+        <v>3485</v>
+      </c>
+      <c r="H1089">
+        <v>50250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1089"/>
+  <dimension ref="A1:H1090"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28710,6 +28710,32 @@
         <v>50250</v>
       </c>
     </row>
+    <row r="1090" spans="1:8">
+      <c r="A1090" s="1">
+        <v>1088</v>
+      </c>
+      <c r="B1090" s="2">
+        <v>46139</v>
+      </c>
+      <c r="C1090">
+        <v>3662</v>
+      </c>
+      <c r="D1090">
+        <v>13212</v>
+      </c>
+      <c r="E1090">
+        <v>1939</v>
+      </c>
+      <c r="F1090">
+        <v>19275</v>
+      </c>
+      <c r="G1090">
+        <v>3444.5</v>
+      </c>
+      <c r="H1090">
+        <v>50300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1090"/>
+  <dimension ref="A1:H1091"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28736,6 +28736,32 @@
         <v>50300</v>
       </c>
     </row>
+    <row r="1091" spans="1:8">
+      <c r="A1091" s="1">
+        <v>1089</v>
+      </c>
+      <c r="B1091" s="2">
+        <v>46140</v>
+      </c>
+      <c r="C1091">
+        <v>3600</v>
+      </c>
+      <c r="D1091">
+        <v>12890.5</v>
+      </c>
+      <c r="E1091">
+        <v>1938</v>
+      </c>
+      <c r="F1091">
+        <v>19050</v>
+      </c>
+      <c r="G1091">
+        <v>3365</v>
+      </c>
+      <c r="H1091">
+        <v>49260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1091"/>
+  <dimension ref="A1:H1092"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28762,6 +28762,32 @@
         <v>49260</v>
       </c>
     </row>
+    <row r="1092" spans="1:8">
+      <c r="A1092" s="1">
+        <v>1090</v>
+      </c>
+      <c r="B1092" s="2">
+        <v>46141</v>
+      </c>
+      <c r="C1092">
+        <v>3604</v>
+      </c>
+      <c r="D1092">
+        <v>12992</v>
+      </c>
+      <c r="E1092">
+        <v>1953.5</v>
+      </c>
+      <c r="F1092">
+        <v>19270</v>
+      </c>
+      <c r="G1092">
+        <v>3331</v>
+      </c>
+      <c r="H1092">
+        <v>49800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1092"/>
+  <dimension ref="A1:H1093"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28788,6 +28788,32 @@
         <v>49800</v>
       </c>
     </row>
+    <row r="1093" spans="1:8">
+      <c r="A1093" s="1">
+        <v>1091</v>
+      </c>
+      <c r="B1093" s="2">
+        <v>46142</v>
+      </c>
+      <c r="C1093">
+        <v>3525.5</v>
+      </c>
+      <c r="D1093">
+        <v>13015.5</v>
+      </c>
+      <c r="E1093">
+        <v>1937.5</v>
+      </c>
+      <c r="F1093">
+        <v>19325</v>
+      </c>
+      <c r="G1093">
+        <v>3363</v>
+      </c>
+      <c r="H1093">
+        <v>49550</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1093"/>
+  <dimension ref="A1:H1094"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28814,6 +28814,32 @@
         <v>49550</v>
       </c>
     </row>
+    <row r="1094" spans="1:8">
+      <c r="A1094" s="1">
+        <v>1092</v>
+      </c>
+      <c r="B1094" s="2">
+        <v>46144</v>
+      </c>
+      <c r="C1094">
+        <v>3584</v>
+      </c>
+      <c r="D1094">
+        <v>12895</v>
+      </c>
+      <c r="E1094">
+        <v>1945</v>
+      </c>
+      <c r="F1094">
+        <v>19180</v>
+      </c>
+      <c r="G1094">
+        <v>3349</v>
+      </c>
+      <c r="H1094">
+        <v>49200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1094"/>
+  <dimension ref="A1:H1095"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28840,6 +28840,32 @@
         <v>49200</v>
       </c>
     </row>
+    <row r="1095" spans="1:8">
+      <c r="A1095" s="1">
+        <v>1093</v>
+      </c>
+      <c r="B1095" s="2">
+        <v>46146</v>
+      </c>
+      <c r="C1095">
+        <v>3584</v>
+      </c>
+      <c r="D1095">
+        <v>12895</v>
+      </c>
+      <c r="E1095">
+        <v>1945</v>
+      </c>
+      <c r="F1095">
+        <v>19180</v>
+      </c>
+      <c r="G1095">
+        <v>3349</v>
+      </c>
+      <c r="H1095">
+        <v>49200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1095"/>
+  <dimension ref="A1:H1096"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28866,6 +28866,32 @@
         <v>49200</v>
       </c>
     </row>
+    <row r="1096" spans="1:8">
+      <c r="A1096" s="1">
+        <v>1094</v>
+      </c>
+      <c r="B1096" s="2">
+        <v>46147</v>
+      </c>
+      <c r="C1096">
+        <v>3632.5</v>
+      </c>
+      <c r="D1096">
+        <v>12970</v>
+      </c>
+      <c r="E1096">
+        <v>1967</v>
+      </c>
+      <c r="F1096">
+        <v>19295</v>
+      </c>
+      <c r="G1096">
+        <v>3348</v>
+      </c>
+      <c r="H1096">
+        <v>49800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -28842,54 +28842,54 @@
     </row>
     <row r="1095" spans="1:8">
       <c r="A1095" s="1">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B1095" s="2">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C1095">
-        <v>3584</v>
+        <v>3632.5</v>
       </c>
       <c r="D1095">
-        <v>12895</v>
+        <v>12970</v>
       </c>
       <c r="E1095">
-        <v>1945</v>
+        <v>1967</v>
       </c>
       <c r="F1095">
-        <v>19180</v>
+        <v>19295</v>
       </c>
       <c r="G1095">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="H1095">
-        <v>49200</v>
+        <v>49800</v>
       </c>
     </row>
     <row r="1096" spans="1:8">
       <c r="A1096" s="1">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B1096" s="2">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="C1096">
-        <v>3632.5</v>
+        <v>3597</v>
       </c>
       <c r="D1096">
-        <v>12970</v>
+        <v>13351.5</v>
       </c>
       <c r="E1096">
-        <v>1967</v>
+        <v>1987</v>
       </c>
       <c r="F1096">
-        <v>19295</v>
+        <v>19450</v>
       </c>
       <c r="G1096">
-        <v>3348</v>
+        <v>3402</v>
       </c>
       <c r="H1096">
-        <v>49800</v>
+        <v>52465</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1096"/>
+  <dimension ref="A1:H1097"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28842,7 +28842,7 @@
     </row>
     <row r="1095" spans="1:8">
       <c r="A1095" s="1">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B1095" s="2">
         <v>46147</v>
@@ -28868,7 +28868,7 @@
     </row>
     <row r="1096" spans="1:8">
       <c r="A1096" s="1">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B1096" s="2">
         <v>46148</v>
@@ -28890,6 +28890,32 @@
       </c>
       <c r="H1096">
         <v>52465</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:8">
+      <c r="A1097" s="1">
+        <v>1095</v>
+      </c>
+      <c r="B1097" s="2">
+        <v>46149</v>
+      </c>
+      <c r="C1097">
+        <v>3559</v>
+      </c>
+      <c r="D1097">
+        <v>13326</v>
+      </c>
+      <c r="E1097">
+        <v>1980</v>
+      </c>
+      <c r="F1097">
+        <v>18825</v>
+      </c>
+      <c r="G1097">
+        <v>3425</v>
+      </c>
+      <c r="H1097">
+        <v>54550</v>
       </c>
     </row>
   </sheetData>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1097"/>
+  <dimension ref="A1:H1098"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28918,6 +28918,32 @@
         <v>54550</v>
       </c>
     </row>
+    <row r="1098" spans="1:8">
+      <c r="A1098" s="1">
+        <v>1096</v>
+      </c>
+      <c r="B1098" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C1098">
+        <v>3560.5</v>
+      </c>
+      <c r="D1098">
+        <v>13445</v>
+      </c>
+      <c r="E1098">
+        <v>1967</v>
+      </c>
+      <c r="F1098">
+        <v>18890</v>
+      </c>
+      <c r="G1098">
+        <v>3417</v>
+      </c>
+      <c r="H1098">
+        <v>53910</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1098"/>
+  <dimension ref="A1:H1099"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28944,6 +28944,32 @@
         <v>53910</v>
       </c>
     </row>
+    <row r="1099" spans="1:8">
+      <c r="A1099" s="1">
+        <v>1097</v>
+      </c>
+      <c r="B1099" s="2">
+        <v>46153</v>
+      </c>
+      <c r="C1099">
+        <v>3655</v>
+      </c>
+      <c r="D1099">
+        <v>13673</v>
+      </c>
+      <c r="E1099">
+        <v>1977</v>
+      </c>
+      <c r="F1099">
+        <v>18955</v>
+      </c>
+      <c r="G1099">
+        <v>3442</v>
+      </c>
+      <c r="H1099">
+        <v>54975</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1099"/>
+  <dimension ref="A1:H1100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28970,6 +28970,32 @@
         <v>54975</v>
       </c>
     </row>
+    <row r="1100" spans="1:8">
+      <c r="A1100" s="1">
+        <v>1098</v>
+      </c>
+      <c r="B1100" s="2">
+        <v>46154</v>
+      </c>
+      <c r="C1100">
+        <v>3639.5</v>
+      </c>
+      <c r="D1100">
+        <v>13872</v>
+      </c>
+      <c r="E1100">
+        <v>2005</v>
+      </c>
+      <c r="F1100">
+        <v>18725</v>
+      </c>
+      <c r="G1100">
+        <v>3498</v>
+      </c>
+      <c r="H1100">
+        <v>55425</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1100"/>
+  <dimension ref="A1:H1101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -28996,6 +28996,32 @@
         <v>55425</v>
       </c>
     </row>
+    <row r="1101" spans="1:8">
+      <c r="A1101" s="1">
+        <v>1099</v>
+      </c>
+      <c r="B1101" s="2">
+        <v>46155</v>
+      </c>
+      <c r="C1101">
+        <v>3729.5</v>
+      </c>
+      <c r="D1101">
+        <v>14097</v>
+      </c>
+      <c r="E1101">
+        <v>2035</v>
+      </c>
+      <c r="F1101">
+        <v>19020</v>
+      </c>
+      <c r="G1101">
+        <v>3517</v>
+      </c>
+      <c r="H1101">
+        <v>55750</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1101"/>
+  <dimension ref="A1:H1102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29022,6 +29022,32 @@
         <v>55750</v>
       </c>
     </row>
+    <row r="1102" spans="1:8">
+      <c r="A1102" s="1">
+        <v>1100</v>
+      </c>
+      <c r="B1102" s="2">
+        <v>46156</v>
+      </c>
+      <c r="C1102">
+        <v>3768</v>
+      </c>
+      <c r="D1102">
+        <v>13986</v>
+      </c>
+      <c r="E1102">
+        <v>2007</v>
+      </c>
+      <c r="F1102">
+        <v>18915</v>
+      </c>
+      <c r="G1102">
+        <v>3596</v>
+      </c>
+      <c r="H1102">
+        <v>55800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1102"/>
+  <dimension ref="A1:H1103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29048,6 +29048,32 @@
         <v>55800</v>
       </c>
     </row>
+    <row r="1103" spans="1:8">
+      <c r="A1103" s="1">
+        <v>1101</v>
+      </c>
+      <c r="B1103" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C1103">
+        <v>3635</v>
+      </c>
+      <c r="D1103">
+        <v>13553.5</v>
+      </c>
+      <c r="E1103">
+        <v>1995</v>
+      </c>
+      <c r="F1103">
+        <v>18390</v>
+      </c>
+      <c r="G1103">
+        <v>3527</v>
+      </c>
+      <c r="H1103">
+        <v>52900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1103"/>
+  <dimension ref="A1:H1104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29074,6 +29074,32 @@
         <v>52900</v>
       </c>
     </row>
+    <row r="1104" spans="1:8">
+      <c r="A1104" s="1">
+        <v>1102</v>
+      </c>
+      <c r="B1104" s="2">
+        <v>46160</v>
+      </c>
+      <c r="C1104">
+        <v>3637</v>
+      </c>
+      <c r="D1104">
+        <v>13428</v>
+      </c>
+      <c r="E1104">
+        <v>1995</v>
+      </c>
+      <c r="F1104">
+        <v>18235</v>
+      </c>
+      <c r="G1104">
+        <v>3529</v>
+      </c>
+      <c r="H1104">
+        <v>52400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1104"/>
+  <dimension ref="A1:H1105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29100,6 +29100,32 @@
         <v>52400</v>
       </c>
     </row>
+    <row r="1105" spans="1:8">
+      <c r="A1105" s="1">
+        <v>1103</v>
+      </c>
+      <c r="B1105" s="2">
+        <v>46161</v>
+      </c>
+      <c r="C1105">
+        <v>3665</v>
+      </c>
+      <c r="D1105">
+        <v>13410</v>
+      </c>
+      <c r="E1105">
+        <v>1967.5</v>
+      </c>
+      <c r="F1105">
+        <v>18800</v>
+      </c>
+      <c r="G1105">
+        <v>3517</v>
+      </c>
+      <c r="H1105">
+        <v>52800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1105"/>
+  <dimension ref="A1:H1106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29126,6 +29126,32 @@
         <v>52800</v>
       </c>
     </row>
+    <row r="1106" spans="1:8">
+      <c r="A1106" s="1">
+        <v>1104</v>
+      </c>
+      <c r="B1106" s="2">
+        <v>46162</v>
+      </c>
+      <c r="C1106">
+        <v>3644</v>
+      </c>
+      <c r="D1106">
+        <v>13418</v>
+      </c>
+      <c r="E1106">
+        <v>1967</v>
+      </c>
+      <c r="F1106">
+        <v>18600</v>
+      </c>
+      <c r="G1106">
+        <v>3519</v>
+      </c>
+      <c r="H1106">
+        <v>54200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1106"/>
+  <dimension ref="A1:H1107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29152,6 +29152,32 @@
         <v>54200</v>
       </c>
     </row>
+    <row r="1107" spans="1:8">
+      <c r="A1107" s="1">
+        <v>1105</v>
+      </c>
+      <c r="B1107" s="2">
+        <v>46163</v>
+      </c>
+      <c r="C1107">
+        <v>3720</v>
+      </c>
+      <c r="D1107">
+        <v>13427</v>
+      </c>
+      <c r="E1107">
+        <v>1997</v>
+      </c>
+      <c r="F1107">
+        <v>18540</v>
+      </c>
+      <c r="G1107">
+        <v>3527.5</v>
+      </c>
+      <c r="H1107">
+        <v>52800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1107"/>
+  <dimension ref="A1:H1108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29178,6 +29178,32 @@
         <v>52800</v>
       </c>
     </row>
+    <row r="1108" spans="1:8">
+      <c r="A1108" s="1">
+        <v>1106</v>
+      </c>
+      <c r="B1108" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C1108">
+        <v>3706</v>
+      </c>
+      <c r="D1108">
+        <v>13545</v>
+      </c>
+      <c r="E1108">
+        <v>2006</v>
+      </c>
+      <c r="F1108">
+        <v>18550</v>
+      </c>
+      <c r="G1108">
+        <v>3544.5</v>
+      </c>
+      <c r="H1108">
+        <v>53900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1108"/>
+  <dimension ref="A1:H1109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29204,6 +29204,32 @@
         <v>53900</v>
       </c>
     </row>
+    <row r="1109" spans="1:8">
+      <c r="A1109" s="1">
+        <v>1107</v>
+      </c>
+      <c r="B1109" s="2">
+        <v>46168</v>
+      </c>
+      <c r="C1109">
+        <v>3759</v>
+      </c>
+      <c r="D1109">
+        <v>13570</v>
+      </c>
+      <c r="E1109">
+        <v>2020</v>
+      </c>
+      <c r="F1109">
+        <v>18560</v>
+      </c>
+      <c r="G1109">
+        <v>3567</v>
+      </c>
+      <c r="H1109">
+        <v>54575</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1109"/>
+  <dimension ref="A1:H1110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29230,6 +29230,32 @@
         <v>54575</v>
       </c>
     </row>
+    <row r="1110" spans="1:8">
+      <c r="A1110" s="1">
+        <v>1108</v>
+      </c>
+      <c r="B1110" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C1110">
+        <v>3738</v>
+      </c>
+      <c r="D1110">
+        <v>13540.5</v>
+      </c>
+      <c r="E1110">
+        <v>2011</v>
+      </c>
+      <c r="F1110">
+        <v>18755</v>
+      </c>
+      <c r="G1110">
+        <v>3516</v>
+      </c>
+      <c r="H1110">
+        <v>54700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1110"/>
+  <dimension ref="A1:H1111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29256,6 +29256,32 @@
         <v>54700</v>
       </c>
     </row>
+    <row r="1111" spans="1:8">
+      <c r="A1111" s="1">
+        <v>1109</v>
+      </c>
+      <c r="B1111" s="2">
+        <v>46170</v>
+      </c>
+      <c r="C1111">
+        <v>3735</v>
+      </c>
+      <c r="D1111">
+        <v>13513</v>
+      </c>
+      <c r="E1111">
+        <v>1985</v>
+      </c>
+      <c r="F1111">
+        <v>18735</v>
+      </c>
+      <c r="G1111">
+        <v>3486</v>
+      </c>
+      <c r="H1111">
+        <v>54900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1111"/>
+  <dimension ref="A1:H1112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29282,6 +29282,32 @@
         <v>54900</v>
       </c>
     </row>
+    <row r="1112" spans="1:8">
+      <c r="A1112" s="1">
+        <v>1110</v>
+      </c>
+      <c r="B1112" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C1112">
+        <v>3769.5</v>
+      </c>
+      <c r="D1112">
+        <v>13615</v>
+      </c>
+      <c r="E1112">
+        <v>2016</v>
+      </c>
+      <c r="F1112">
+        <v>18875</v>
+      </c>
+      <c r="G1112">
+        <v>3549</v>
+      </c>
+      <c r="H1112">
+        <v>55010</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1112"/>
+  <dimension ref="A1:H1113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29308,6 +29308,32 @@
         <v>55010</v>
       </c>
     </row>
+    <row r="1113" spans="1:8">
+      <c r="A1113" s="1">
+        <v>1111</v>
+      </c>
+      <c r="B1113" s="2">
+        <v>46174</v>
+      </c>
+      <c r="C1113">
+        <v>3795.5</v>
+      </c>
+      <c r="D1113">
+        <v>13819</v>
+      </c>
+      <c r="E1113">
+        <v>2008</v>
+      </c>
+      <c r="F1113">
+        <v>19050</v>
+      </c>
+      <c r="G1113">
+        <v>3555</v>
+      </c>
+      <c r="H1113">
+        <v>56400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1113"/>
+  <dimension ref="A1:H1114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29334,6 +29334,32 @@
         <v>56400</v>
       </c>
     </row>
+    <row r="1114" spans="1:8">
+      <c r="A1114" s="1">
+        <v>1112</v>
+      </c>
+      <c r="B1114" s="2">
+        <v>46175</v>
+      </c>
+      <c r="C1114">
+        <v>3855</v>
+      </c>
+      <c r="D1114">
+        <v>13966</v>
+      </c>
+      <c r="E1114">
+        <v>2025</v>
+      </c>
+      <c r="F1114">
+        <v>19170</v>
+      </c>
+      <c r="G1114">
+        <v>3612</v>
+      </c>
+      <c r="H1114">
+        <v>57525</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1114"/>
+  <dimension ref="A1:H1115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29360,6 +29360,32 @@
         <v>57525</v>
       </c>
     </row>
+    <row r="1115" spans="1:8">
+      <c r="A1115" s="1">
+        <v>1113</v>
+      </c>
+      <c r="B1115" s="2">
+        <v>46176</v>
+      </c>
+      <c r="C1115">
+        <v>3797</v>
+      </c>
+      <c r="D1115">
+        <v>13920.5</v>
+      </c>
+      <c r="E1115">
+        <v>2035</v>
+      </c>
+      <c r="F1115">
+        <v>18810</v>
+      </c>
+      <c r="G1115">
+        <v>3624.5</v>
+      </c>
+      <c r="H1115">
+        <v>57110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1115"/>
+  <dimension ref="A1:H1116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29386,6 +29386,32 @@
         <v>57110</v>
       </c>
     </row>
+    <row r="1116" spans="1:8">
+      <c r="A1116" s="1">
+        <v>1114</v>
+      </c>
+      <c r="B1116" s="2">
+        <v>46177</v>
+      </c>
+      <c r="C1116">
+        <v>3739</v>
+      </c>
+      <c r="D1116">
+        <v>13872</v>
+      </c>
+      <c r="E1116">
+        <v>2015</v>
+      </c>
+      <c r="F1116">
+        <v>18375</v>
+      </c>
+      <c r="G1116">
+        <v>3564</v>
+      </c>
+      <c r="H1116">
+        <v>55600</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1116"/>
+  <dimension ref="A1:H1117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29412,6 +29412,32 @@
         <v>55600</v>
       </c>
     </row>
+    <row r="1117" spans="1:8">
+      <c r="A1117" s="1">
+        <v>1115</v>
+      </c>
+      <c r="B1117" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C1117">
+        <v>3736</v>
+      </c>
+      <c r="D1117">
+        <v>13731</v>
+      </c>
+      <c r="E1117">
+        <v>2003</v>
+      </c>
+      <c r="F1117">
+        <v>18545</v>
+      </c>
+      <c r="G1117">
+        <v>3575</v>
+      </c>
+      <c r="H1117">
+        <v>54000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1117"/>
+  <dimension ref="A1:H1118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29438,6 +29438,32 @@
         <v>54000</v>
       </c>
     </row>
+    <row r="1118" spans="1:8">
+      <c r="A1118" s="1">
+        <v>1116</v>
+      </c>
+      <c r="B1118" s="2">
+        <v>46182</v>
+      </c>
+      <c r="C1118">
+        <v>3608</v>
+      </c>
+      <c r="D1118">
+        <v>13716</v>
+      </c>
+      <c r="E1118">
+        <v>1983</v>
+      </c>
+      <c r="F1118">
+        <v>17930</v>
+      </c>
+      <c r="G1118">
+        <v>3576</v>
+      </c>
+      <c r="H1118">
+        <v>53060</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1118"/>
+  <dimension ref="A1:H1119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29464,6 +29464,32 @@
         <v>53060</v>
       </c>
     </row>
+    <row r="1119" spans="1:8">
+      <c r="A1119" s="1">
+        <v>1117</v>
+      </c>
+      <c r="B1119" s="2">
+        <v>46183</v>
+      </c>
+      <c r="C1119">
+        <v>3489</v>
+      </c>
+      <c r="D1119">
+        <v>13370</v>
+      </c>
+      <c r="E1119">
+        <v>1974.5</v>
+      </c>
+      <c r="F1119">
+        <v>17380</v>
+      </c>
+      <c r="G1119">
+        <v>3486</v>
+      </c>
+      <c r="H1119">
+        <v>51750</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1119"/>
+  <dimension ref="A1:H1120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29490,6 +29490,32 @@
         <v>51750</v>
       </c>
     </row>
+    <row r="1120" spans="1:8">
+      <c r="A1120" s="1">
+        <v>1118</v>
+      </c>
+      <c r="B1120" s="2">
+        <v>46184</v>
+      </c>
+      <c r="C1120">
+        <v>3498.5</v>
+      </c>
+      <c r="D1120">
+        <v>13420</v>
+      </c>
+      <c r="E1120">
+        <v>1967</v>
+      </c>
+      <c r="F1120">
+        <v>17440</v>
+      </c>
+      <c r="G1120">
+        <v>3468</v>
+      </c>
+      <c r="H1120">
+        <v>52395</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1120"/>
+  <dimension ref="A1:H1121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29516,6 +29516,32 @@
         <v>52395</v>
       </c>
     </row>
+    <row r="1121" spans="1:8">
+      <c r="A1121" s="1">
+        <v>1119</v>
+      </c>
+      <c r="B1121" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C1121">
+        <v>3536</v>
+      </c>
+      <c r="D1121">
+        <v>13603</v>
+      </c>
+      <c r="E1121">
+        <v>1957</v>
+      </c>
+      <c r="F1121">
+        <v>17630</v>
+      </c>
+      <c r="G1121">
+        <v>3557</v>
+      </c>
+      <c r="H1121">
+        <v>53350</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1121"/>
+  <dimension ref="A1:H1122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29542,6 +29542,32 @@
         <v>53350</v>
       </c>
     </row>
+    <row r="1122" spans="1:8">
+      <c r="A1122" s="1">
+        <v>1120</v>
+      </c>
+      <c r="B1122" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C1122">
+        <v>3419.5</v>
+      </c>
+      <c r="D1122">
+        <v>13714</v>
+      </c>
+      <c r="E1122">
+        <v>1964</v>
+      </c>
+      <c r="F1122">
+        <v>17810</v>
+      </c>
+      <c r="G1122">
+        <v>3562</v>
+      </c>
+      <c r="H1122">
+        <v>54650</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1122"/>
+  <dimension ref="A1:H1123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29568,6 +29568,32 @@
         <v>54650</v>
       </c>
     </row>
+    <row r="1123" spans="1:8">
+      <c r="A1123" s="1">
+        <v>1121</v>
+      </c>
+      <c r="B1123" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C1123">
+        <v>3359</v>
+      </c>
+      <c r="D1123">
+        <v>13682</v>
+      </c>
+      <c r="E1123">
+        <v>1956</v>
+      </c>
+      <c r="F1123">
+        <v>17630</v>
+      </c>
+      <c r="G1123">
+        <v>3550</v>
+      </c>
+      <c r="H1123">
+        <v>55150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1123"/>
+  <dimension ref="A1:H1124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29594,6 +29594,32 @@
         <v>55150</v>
       </c>
     </row>
+    <row r="1124" spans="1:8">
+      <c r="A1124" s="1">
+        <v>1122</v>
+      </c>
+      <c r="B1124" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C1124">
+        <v>3405.5</v>
+      </c>
+      <c r="D1124">
+        <v>13736</v>
+      </c>
+      <c r="E1124">
+        <v>1945</v>
+      </c>
+      <c r="F1124">
+        <v>17820</v>
+      </c>
+      <c r="G1124">
+        <v>3592</v>
+      </c>
+      <c r="H1124">
+        <v>55400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1124"/>
+  <dimension ref="A1:H1125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29620,6 +29620,32 @@
         <v>55400</v>
       </c>
     </row>
+    <row r="1125" spans="1:8">
+      <c r="A1125" s="1">
+        <v>1123</v>
+      </c>
+      <c r="B1125" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C1125">
+        <v>3402</v>
+      </c>
+      <c r="D1125">
+        <v>13612</v>
+      </c>
+      <c r="E1125">
+        <v>1945</v>
+      </c>
+      <c r="F1125">
+        <v>17770</v>
+      </c>
+      <c r="G1125">
+        <v>3565</v>
+      </c>
+      <c r="H1125">
+        <v>53455</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1125"/>
+  <dimension ref="A1:H1126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29646,6 +29646,32 @@
         <v>53455</v>
       </c>
     </row>
+    <row r="1126" spans="1:8">
+      <c r="A1126" s="1">
+        <v>1124</v>
+      </c>
+      <c r="B1126" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C1126">
+        <v>3400</v>
+      </c>
+      <c r="D1126">
+        <v>13530.5</v>
+      </c>
+      <c r="E1126">
+        <v>1935</v>
+      </c>
+      <c r="F1126">
+        <v>17590</v>
+      </c>
+      <c r="G1126">
+        <v>3584.5</v>
+      </c>
+      <c r="H1126">
+        <v>53200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1126"/>
+  <dimension ref="A1:H1127"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29672,6 +29672,32 @@
         <v>53200</v>
       </c>
     </row>
+    <row r="1127" spans="1:8">
+      <c r="A1127" s="1">
+        <v>1125</v>
+      </c>
+      <c r="B1127" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C1127">
+        <v>3405</v>
+      </c>
+      <c r="D1127">
+        <v>13642</v>
+      </c>
+      <c r="E1127">
+        <v>1928.5</v>
+      </c>
+      <c r="F1127">
+        <v>17640</v>
+      </c>
+      <c r="G1127">
+        <v>3612.5</v>
+      </c>
+      <c r="H1127">
+        <v>54995</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1127"/>
+  <dimension ref="A1:H1128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29698,6 +29698,32 @@
         <v>54995</v>
       </c>
     </row>
+    <row r="1128" spans="1:8">
+      <c r="A1128" s="1">
+        <v>1126</v>
+      </c>
+      <c r="B1128" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C1128">
+        <v>3263.5</v>
+      </c>
+      <c r="D1128">
+        <v>13334</v>
+      </c>
+      <c r="E1128">
+        <v>1910</v>
+      </c>
+      <c r="F1128">
+        <v>17105</v>
+      </c>
+      <c r="G1128">
+        <v>3503</v>
+      </c>
+      <c r="H1128">
+        <v>51900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1128"/>
+  <dimension ref="A1:H1129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29724,6 +29724,32 @@
         <v>51900</v>
       </c>
     </row>
+    <row r="1129" spans="1:8">
+      <c r="A1129" s="1">
+        <v>1127</v>
+      </c>
+      <c r="B1129" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C1129">
+        <v>3150</v>
+      </c>
+      <c r="D1129">
+        <v>13181.5</v>
+      </c>
+      <c r="E1129">
+        <v>1896</v>
+      </c>
+      <c r="F1129">
+        <v>16610</v>
+      </c>
+      <c r="G1129">
+        <v>3437</v>
+      </c>
+      <c r="H1129">
+        <v>49550</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1129"/>
+  <dimension ref="A1:H1130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29750,6 +29750,32 @@
         <v>49550</v>
       </c>
     </row>
+    <row r="1130" spans="1:8">
+      <c r="A1130" s="1">
+        <v>1128</v>
+      </c>
+      <c r="B1130" s="2">
+        <v>46198</v>
+      </c>
+      <c r="C1130">
+        <v>3132</v>
+      </c>
+      <c r="D1130">
+        <v>13194</v>
+      </c>
+      <c r="E1130">
+        <v>1894</v>
+      </c>
+      <c r="F1130">
+        <v>16660</v>
+      </c>
+      <c r="G1130">
+        <v>3432</v>
+      </c>
+      <c r="H1130">
+        <v>50100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1130"/>
+  <dimension ref="A1:H1131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29776,6 +29776,32 @@
         <v>50100</v>
       </c>
     </row>
+    <row r="1131" spans="1:8">
+      <c r="A1131" s="1">
+        <v>1129</v>
+      </c>
+      <c r="B1131" s="2">
+        <v>46199</v>
+      </c>
+      <c r="C1131">
+        <v>3164</v>
+      </c>
+      <c r="D1131">
+        <v>13287</v>
+      </c>
+      <c r="E1131">
+        <v>1880</v>
+      </c>
+      <c r="F1131">
+        <v>16570</v>
+      </c>
+      <c r="G1131">
+        <v>3460</v>
+      </c>
+      <c r="H1131">
+        <v>50325</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1131"/>
+  <dimension ref="A1:H1132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29802,6 +29802,32 @@
         <v>50325</v>
       </c>
     </row>
+    <row r="1132" spans="1:8">
+      <c r="A1132" s="1">
+        <v>1130</v>
+      </c>
+      <c r="B1132" s="2">
+        <v>46202</v>
+      </c>
+      <c r="C1132">
+        <v>3160.5</v>
+      </c>
+      <c r="D1132">
+        <v>13302.5</v>
+      </c>
+      <c r="E1132">
+        <v>1871.5</v>
+      </c>
+      <c r="F1132">
+        <v>16455</v>
+      </c>
+      <c r="G1132">
+        <v>3491</v>
+      </c>
+      <c r="H1132">
+        <v>51000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1132"/>
+  <dimension ref="A1:H1133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29828,6 +29828,32 @@
         <v>51000</v>
       </c>
     </row>
+    <row r="1133" spans="1:8">
+      <c r="A1133" s="1">
+        <v>1131</v>
+      </c>
+      <c r="B1133" s="2">
+        <v>46203</v>
+      </c>
+      <c r="C1133">
+        <v>3105.5</v>
+      </c>
+      <c r="D1133">
+        <v>13341</v>
+      </c>
+      <c r="E1133">
+        <v>1845</v>
+      </c>
+      <c r="F1133">
+        <v>16275</v>
+      </c>
+      <c r="G1133">
+        <v>3565.5</v>
+      </c>
+      <c r="H1133">
+        <v>51100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1135"/>
+  <dimension ref="A1:H1136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29906,6 +29906,32 @@
         <v>51150</v>
       </c>
     </row>
+    <row r="1136" spans="1:8">
+      <c r="A1136" s="1">
+        <v>1134</v>
+      </c>
+      <c r="B1136" s="2">
+        <v>46205</v>
+      </c>
+      <c r="C1136">
+        <v>3061.5</v>
+      </c>
+      <c r="D1136">
+        <v>13202</v>
+      </c>
+      <c r="E1136">
+        <v>1828.5</v>
+      </c>
+      <c r="F1136">
+        <v>16070</v>
+      </c>
+      <c r="G1136">
+        <v>3475</v>
+      </c>
+      <c r="H1136">
+        <v>51200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1136"/>
+  <dimension ref="A1:H1137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29932,6 +29932,32 @@
         <v>51200</v>
       </c>
     </row>
+    <row r="1137" spans="1:8">
+      <c r="A1137" s="1">
+        <v>1135</v>
+      </c>
+      <c r="B1137" s="2">
+        <v>46206</v>
+      </c>
+      <c r="C1137">
+        <v>3080</v>
+      </c>
+      <c r="D1137">
+        <v>13298.5</v>
+      </c>
+      <c r="E1137">
+        <v>1851</v>
+      </c>
+      <c r="F1137">
+        <v>16115</v>
+      </c>
+      <c r="G1137">
+        <v>3546</v>
+      </c>
+      <c r="H1137">
+        <v>52000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1137"/>
+  <dimension ref="A1:H1138"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29958,6 +29958,32 @@
         <v>52000</v>
       </c>
     </row>
+    <row r="1138" spans="1:8">
+      <c r="A1138" s="1">
+        <v>1136</v>
+      </c>
+      <c r="B1138" s="2">
+        <v>46209</v>
+      </c>
+      <c r="C1138">
+        <v>3105</v>
+      </c>
+      <c r="D1138">
+        <v>13310</v>
+      </c>
+      <c r="E1138">
+        <v>1852.5</v>
+      </c>
+      <c r="F1138">
+        <v>16065</v>
+      </c>
+      <c r="G1138">
+        <v>3599</v>
+      </c>
+      <c r="H1138">
+        <v>52525</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1138"/>
+  <dimension ref="A1:H1139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -29984,6 +29984,32 @@
         <v>52525</v>
       </c>
     </row>
+    <row r="1139" spans="1:8">
+      <c r="A1139" s="1">
+        <v>1137</v>
+      </c>
+      <c r="B1139" s="2">
+        <v>46210</v>
+      </c>
+      <c r="C1139">
+        <v>3119</v>
+      </c>
+      <c r="D1139">
+        <v>13309</v>
+      </c>
+      <c r="E1139">
+        <v>1849</v>
+      </c>
+      <c r="F1139">
+        <v>16160</v>
+      </c>
+      <c r="G1139">
+        <v>3560</v>
+      </c>
+      <c r="H1139">
+        <v>52900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1139"/>
+  <dimension ref="A1:H1140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30010,6 +30010,32 @@
         <v>52900</v>
       </c>
     </row>
+    <row r="1140" spans="1:8">
+      <c r="A1140" s="1">
+        <v>1138</v>
+      </c>
+      <c r="B1140" s="2">
+        <v>46211</v>
+      </c>
+      <c r="C1140">
+        <v>3141</v>
+      </c>
+      <c r="D1140">
+        <v>13090</v>
+      </c>
+      <c r="E1140">
+        <v>1851</v>
+      </c>
+      <c r="F1140">
+        <v>16160</v>
+      </c>
+      <c r="G1140">
+        <v>3529</v>
+      </c>
+      <c r="H1140">
+        <v>52350</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1140"/>
+  <dimension ref="A1:H1141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30036,6 +30036,32 @@
         <v>52350</v>
       </c>
     </row>
+    <row r="1141" spans="1:8">
+      <c r="A1141" s="1">
+        <v>1139</v>
+      </c>
+      <c r="B1141" s="2">
+        <v>46212</v>
+      </c>
+      <c r="C1141">
+        <v>3164</v>
+      </c>
+      <c r="D1141">
+        <v>13356.5</v>
+      </c>
+      <c r="E1141">
+        <v>1850</v>
+      </c>
+      <c r="F1141">
+        <v>16355</v>
+      </c>
+      <c r="G1141">
+        <v>3622</v>
+      </c>
+      <c r="H1141">
+        <v>53450</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1141"/>
+  <dimension ref="A1:H1142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30062,6 +30062,32 @@
         <v>53450</v>
       </c>
     </row>
+    <row r="1142" spans="1:8">
+      <c r="A1142" s="1">
+        <v>1140</v>
+      </c>
+      <c r="B1142" s="2">
+        <v>46213</v>
+      </c>
+      <c r="C1142">
+        <v>3156</v>
+      </c>
+      <c r="D1142">
+        <v>13408.5</v>
+      </c>
+      <c r="E1142">
+        <v>1851</v>
+      </c>
+      <c r="F1142">
+        <v>16410</v>
+      </c>
+      <c r="G1142">
+        <v>3602</v>
+      </c>
+      <c r="H1142">
+        <v>52575</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1142"/>
+  <dimension ref="A1:H1143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30088,6 +30088,32 @@
         <v>52575</v>
       </c>
     </row>
+    <row r="1143" spans="1:8">
+      <c r="A1143" s="1">
+        <v>1141</v>
+      </c>
+      <c r="B1143" s="2">
+        <v>46216</v>
+      </c>
+      <c r="C1143">
+        <v>3138.5</v>
+      </c>
+      <c r="D1143">
+        <v>13460.5</v>
+      </c>
+      <c r="E1143">
+        <v>1832</v>
+      </c>
+      <c r="F1143">
+        <v>16405</v>
+      </c>
+      <c r="G1143">
+        <v>3571</v>
+      </c>
+      <c r="H1143">
+        <v>52705</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1143"/>
+  <dimension ref="A1:H1144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30114,6 +30114,32 @@
         <v>52705</v>
       </c>
     </row>
+    <row r="1144" spans="1:8">
+      <c r="A1144" s="1">
+        <v>1142</v>
+      </c>
+      <c r="B1144" s="2">
+        <v>46217</v>
+      </c>
+      <c r="C1144">
+        <v>3171</v>
+      </c>
+      <c r="D1144">
+        <v>13541</v>
+      </c>
+      <c r="E1144">
+        <v>1803</v>
+      </c>
+      <c r="F1144">
+        <v>16590</v>
+      </c>
+      <c r="G1144">
+        <v>3589.5</v>
+      </c>
+      <c r="H1144">
+        <v>53900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1144"/>
+  <dimension ref="A1:H1145"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30140,6 +30140,32 @@
         <v>53900</v>
       </c>
     </row>
+    <row r="1145" spans="1:8">
+      <c r="A1145" s="1">
+        <v>1143</v>
+      </c>
+      <c r="B1145" s="2">
+        <v>46218</v>
+      </c>
+      <c r="C1145">
+        <v>3153.5</v>
+      </c>
+      <c r="D1145">
+        <v>13537</v>
+      </c>
+      <c r="E1145">
+        <v>1797</v>
+      </c>
+      <c r="F1145">
+        <v>16505</v>
+      </c>
+      <c r="G1145">
+        <v>3553.5</v>
+      </c>
+      <c r="H1145">
+        <v>52705</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1145"/>
+  <dimension ref="A1:H1146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30166,6 +30166,32 @@
         <v>52705</v>
       </c>
     </row>
+    <row r="1146" spans="1:8">
+      <c r="A1146" s="1">
+        <v>1144</v>
+      </c>
+      <c r="B1146" s="2">
+        <v>46219</v>
+      </c>
+      <c r="C1146">
+        <v>3170</v>
+      </c>
+      <c r="D1146">
+        <v>13565</v>
+      </c>
+      <c r="E1146">
+        <v>1827.5</v>
+      </c>
+      <c r="F1146">
+        <v>17150</v>
+      </c>
+      <c r="G1146">
+        <v>3591</v>
+      </c>
+      <c r="H1146">
+        <v>52860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1146"/>
+  <dimension ref="A1:H1147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30192,6 +30192,32 @@
         <v>52860</v>
       </c>
     </row>
+    <row r="1147" spans="1:8">
+      <c r="A1147" s="1">
+        <v>1145</v>
+      </c>
+      <c r="B1147" s="2">
+        <v>46220</v>
+      </c>
+      <c r="C1147">
+        <v>3154</v>
+      </c>
+      <c r="D1147">
+        <v>13373.5</v>
+      </c>
+      <c r="E1147">
+        <v>1821</v>
+      </c>
+      <c r="F1147">
+        <v>16725</v>
+      </c>
+      <c r="G1147">
+        <v>3549</v>
+      </c>
+      <c r="H1147">
+        <v>52045</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1147"/>
+  <dimension ref="A1:H1148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30218,6 +30218,32 @@
         <v>52045</v>
       </c>
     </row>
+    <row r="1148" spans="1:8">
+      <c r="A1148" s="1">
+        <v>1146</v>
+      </c>
+      <c r="B1148" s="2">
+        <v>46223</v>
+      </c>
+      <c r="C1148">
+        <v>3156</v>
+      </c>
+      <c r="D1148">
+        <v>13629</v>
+      </c>
+      <c r="E1148">
+        <v>1830</v>
+      </c>
+      <c r="F1148">
+        <v>16850</v>
+      </c>
+      <c r="G1148">
+        <v>3575</v>
+      </c>
+      <c r="H1148">
+        <v>53300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1148"/>
+  <dimension ref="A1:H1149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30244,6 +30244,32 @@
         <v>53300</v>
       </c>
     </row>
+    <row r="1149" spans="1:8">
+      <c r="A1149" s="1">
+        <v>1147</v>
+      </c>
+      <c r="B1149" s="2">
+        <v>46224</v>
+      </c>
+      <c r="C1149">
+        <v>3183.5</v>
+      </c>
+      <c r="D1149">
+        <v>13856</v>
+      </c>
+      <c r="E1149">
+        <v>1842</v>
+      </c>
+      <c r="F1149">
+        <v>16970</v>
+      </c>
+      <c r="G1149">
+        <v>3591</v>
+      </c>
+      <c r="H1149">
+        <v>54100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1149"/>
+  <dimension ref="A1:H1150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30270,6 +30270,32 @@
         <v>54100</v>
       </c>
     </row>
+    <row r="1150" spans="1:8">
+      <c r="A1150" s="1">
+        <v>1148</v>
+      </c>
+      <c r="B1150" s="2">
+        <v>46225</v>
+      </c>
+      <c r="C1150">
+        <v>3205</v>
+      </c>
+      <c r="D1150">
+        <v>13895</v>
+      </c>
+      <c r="E1150">
+        <v>1841.5</v>
+      </c>
+      <c r="F1150">
+        <v>16940</v>
+      </c>
+      <c r="G1150">
+        <v>3614</v>
+      </c>
+      <c r="H1150">
+        <v>53900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1150"/>
+  <dimension ref="A1:H1151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30296,6 +30296,32 @@
         <v>53900</v>
       </c>
     </row>
+    <row r="1151" spans="1:8">
+      <c r="A1151" s="1">
+        <v>1149</v>
+      </c>
+      <c r="B1151" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C1151">
+        <v>3194</v>
+      </c>
+      <c r="D1151">
+        <v>13745</v>
+      </c>
+      <c r="E1151">
+        <v>1875</v>
+      </c>
+      <c r="F1151">
+        <v>17200</v>
+      </c>
+      <c r="G1151">
+        <v>3653</v>
+      </c>
+      <c r="H1151">
+        <v>53800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1151"/>
+  <dimension ref="A1:H1152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30322,6 +30322,32 @@
         <v>53800</v>
       </c>
     </row>
+    <row r="1152" spans="1:8">
+      <c r="A1152" s="1">
+        <v>1150</v>
+      </c>
+      <c r="B1152" s="2">
+        <v>46227</v>
+      </c>
+      <c r="C1152">
+        <v>3175</v>
+      </c>
+      <c r="D1152">
+        <v>13617</v>
+      </c>
+      <c r="E1152">
+        <v>1865.5</v>
+      </c>
+      <c r="F1152">
+        <v>17205</v>
+      </c>
+      <c r="G1152">
+        <v>3633</v>
+      </c>
+      <c r="H1152">
+        <v>53250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1152"/>
+  <dimension ref="A1:H1153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30348,6 +30348,32 @@
         <v>53250</v>
       </c>
     </row>
+    <row r="1153" spans="1:8">
+      <c r="A1153" s="1">
+        <v>1151</v>
+      </c>
+      <c r="B1153" s="2">
+        <v>46230</v>
+      </c>
+      <c r="C1153">
+        <v>3192</v>
+      </c>
+      <c r="D1153">
+        <v>13810</v>
+      </c>
+      <c r="E1153">
+        <v>1859</v>
+      </c>
+      <c r="F1153">
+        <v>17165</v>
+      </c>
+      <c r="G1153">
+        <v>3685.5</v>
+      </c>
+      <c r="H1153">
+        <v>54250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1153"/>
+  <dimension ref="A1:H1154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30374,6 +30374,32 @@
         <v>54250</v>
       </c>
     </row>
+    <row r="1154" spans="1:8">
+      <c r="A1154" s="1">
+        <v>1152</v>
+      </c>
+      <c r="B1154" s="2">
+        <v>46231</v>
+      </c>
+      <c r="C1154">
+        <v>3159.5</v>
+      </c>
+      <c r="D1154">
+        <v>13643.5</v>
+      </c>
+      <c r="E1154">
+        <v>1856</v>
+      </c>
+      <c r="F1154">
+        <v>16860</v>
+      </c>
+      <c r="G1154">
+        <v>3631.5</v>
+      </c>
+      <c r="H1154">
+        <v>53600</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1154"/>
+  <dimension ref="A1:H1155"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30400,6 +30400,32 @@
         <v>53600</v>
       </c>
     </row>
+    <row r="1155" spans="1:8">
+      <c r="A1155" s="1">
+        <v>1153</v>
+      </c>
+      <c r="B1155" s="2">
+        <v>46232</v>
+      </c>
+      <c r="C1155">
+        <v>3207</v>
+      </c>
+      <c r="D1155">
+        <v>13633</v>
+      </c>
+      <c r="E1155">
+        <v>1877</v>
+      </c>
+      <c r="F1155">
+        <v>17000</v>
+      </c>
+      <c r="G1155">
+        <v>3639</v>
+      </c>
+      <c r="H1155">
+        <v>53990</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1155"/>
+  <dimension ref="A1:H1156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30426,6 +30426,32 @@
         <v>53990</v>
       </c>
     </row>
+    <row r="1156" spans="1:8">
+      <c r="A1156" s="1">
+        <v>1154</v>
+      </c>
+      <c r="B1156" s="2">
+        <v>46233</v>
+      </c>
+      <c r="C1156">
+        <v>3231</v>
+      </c>
+      <c r="D1156">
+        <v>13795</v>
+      </c>
+      <c r="E1156">
+        <v>1863</v>
+      </c>
+      <c r="F1156">
+        <v>16945</v>
+      </c>
+      <c r="G1156">
+        <v>3662</v>
+      </c>
+      <c r="H1156">
+        <v>54125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1156"/>
+  <dimension ref="A1:H1157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30452,6 +30452,32 @@
         <v>54125</v>
       </c>
     </row>
+    <row r="1157" spans="1:8">
+      <c r="A1157" s="1">
+        <v>1155</v>
+      </c>
+      <c r="B1157" s="2">
+        <v>46234</v>
+      </c>
+      <c r="C1157">
+        <v>3196</v>
+      </c>
+      <c r="D1157">
+        <v>13834</v>
+      </c>
+      <c r="E1157">
+        <v>1851.5</v>
+      </c>
+      <c r="F1157">
+        <v>17100</v>
+      </c>
+      <c r="G1157">
+        <v>3710.5</v>
+      </c>
+      <c r="H1157">
+        <v>54660</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1157"/>
+  <dimension ref="A1:H1158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30478,6 +30478,32 @@
         <v>54660</v>
       </c>
     </row>
+    <row r="1158" spans="1:8">
+      <c r="A1158" s="1">
+        <v>1156</v>
+      </c>
+      <c r="B1158" s="2">
+        <v>46237</v>
+      </c>
+      <c r="C1158">
+        <v>3260</v>
+      </c>
+      <c r="D1158">
+        <v>13945</v>
+      </c>
+      <c r="E1158">
+        <v>1828</v>
+      </c>
+      <c r="F1158">
+        <v>16785</v>
+      </c>
+      <c r="G1158">
+        <v>3751</v>
+      </c>
+      <c r="H1158">
+        <v>55200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1158"/>
+  <dimension ref="A1:H1159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30504,6 +30504,32 @@
         <v>55200</v>
       </c>
     </row>
+    <row r="1159" spans="1:8">
+      <c r="A1159" s="1">
+        <v>1157</v>
+      </c>
+      <c r="B1159" s="2">
+        <v>46238</v>
+      </c>
+      <c r="C1159">
+        <v>3271</v>
+      </c>
+      <c r="D1159">
+        <v>14195</v>
+      </c>
+      <c r="E1159">
+        <v>1847</v>
+      </c>
+      <c r="F1159">
+        <v>17125</v>
+      </c>
+      <c r="G1159">
+        <v>3730</v>
+      </c>
+      <c r="H1159">
+        <v>55700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1159"/>
+  <dimension ref="A1:H1160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30530,6 +30530,32 @@
         <v>55700</v>
       </c>
     </row>
+    <row r="1160" spans="1:8">
+      <c r="A1160" s="1">
+        <v>1158</v>
+      </c>
+      <c r="B1160" s="2">
+        <v>46239</v>
+      </c>
+      <c r="C1160">
+        <v>3229</v>
+      </c>
+      <c r="D1160">
+        <v>14167.5</v>
+      </c>
+      <c r="E1160">
+        <v>1845</v>
+      </c>
+      <c r="F1160">
+        <v>16915</v>
+      </c>
+      <c r="G1160">
+        <v>3737</v>
+      </c>
+      <c r="H1160">
+        <v>56225</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1160"/>
+  <dimension ref="A1:H1161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30556,6 +30556,32 @@
         <v>56225</v>
       </c>
     </row>
+    <row r="1161" spans="1:8">
+      <c r="A1161" s="1">
+        <v>1159</v>
+      </c>
+      <c r="B1161" s="2">
+        <v>46240</v>
+      </c>
+      <c r="C1161">
+        <v>3261</v>
+      </c>
+      <c r="D1161">
+        <v>14455</v>
+      </c>
+      <c r="E1161">
+        <v>1851</v>
+      </c>
+      <c r="F1161">
+        <v>16595</v>
+      </c>
+      <c r="G1161">
+        <v>3857</v>
+      </c>
+      <c r="H1161">
+        <v>56500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1161"/>
+  <dimension ref="A1:H1162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30582,6 +30582,32 @@
         <v>56500</v>
       </c>
     </row>
+    <row r="1162" spans="1:8">
+      <c r="A1162" s="1">
+        <v>1160</v>
+      </c>
+      <c r="B1162" s="2">
+        <v>46241</v>
+      </c>
+      <c r="C1162">
+        <v>3279.5</v>
+      </c>
+      <c r="D1162">
+        <v>14240</v>
+      </c>
+      <c r="E1162">
+        <v>1840.5</v>
+      </c>
+      <c r="F1162">
+        <v>16745</v>
+      </c>
+      <c r="G1162">
+        <v>3785</v>
+      </c>
+      <c r="H1162">
+        <v>56100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1162"/>
+  <dimension ref="A1:H1163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30608,6 +30608,32 @@
         <v>56100</v>
       </c>
     </row>
+    <row r="1163" spans="1:8">
+      <c r="A1163" s="1">
+        <v>1161</v>
+      </c>
+      <c r="B1163" s="2">
+        <v>46244</v>
+      </c>
+      <c r="C1163">
+        <v>3327.5</v>
+      </c>
+      <c r="D1163">
+        <v>14290</v>
+      </c>
+      <c r="E1163">
+        <v>1858</v>
+      </c>
+      <c r="F1163">
+        <v>16775</v>
+      </c>
+      <c r="G1163">
+        <v>3786</v>
+      </c>
+      <c r="H1163">
+        <v>55900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1163"/>
+  <dimension ref="A1:H1164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30634,6 +30634,32 @@
         <v>55900</v>
       </c>
     </row>
+    <row r="1164" spans="1:8">
+      <c r="A1164" s="1">
+        <v>1162</v>
+      </c>
+      <c r="B1164" s="2">
+        <v>46245</v>
+      </c>
+      <c r="C1164">
+        <v>3373</v>
+      </c>
+      <c r="D1164">
+        <v>14424.5</v>
+      </c>
+      <c r="E1164">
+        <v>1878</v>
+      </c>
+      <c r="F1164">
+        <v>16640</v>
+      </c>
+      <c r="G1164">
+        <v>3822</v>
+      </c>
+      <c r="H1164">
+        <v>55305</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1164"/>
+  <dimension ref="A1:H1165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30660,6 +30660,32 @@
         <v>55305</v>
       </c>
     </row>
+    <row r="1165" spans="1:8">
+      <c r="A1165" s="1">
+        <v>1163</v>
+      </c>
+      <c r="B1165" s="2">
+        <v>46246</v>
+      </c>
+      <c r="C1165">
+        <v>3307.5</v>
+      </c>
+      <c r="D1165">
+        <v>14376</v>
+      </c>
+      <c r="E1165">
+        <v>1880</v>
+      </c>
+      <c r="F1165">
+        <v>16725</v>
+      </c>
+      <c r="G1165">
+        <v>3852</v>
+      </c>
+      <c r="H1165">
+        <v>56050</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1165"/>
+  <dimension ref="A1:H1166"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30686,6 +30686,32 @@
         <v>56050</v>
       </c>
     </row>
+    <row r="1166" spans="1:8">
+      <c r="A1166" s="1">
+        <v>1164</v>
+      </c>
+      <c r="B1166" s="2">
+        <v>46247</v>
+      </c>
+      <c r="C1166">
+        <v>3279</v>
+      </c>
+      <c r="D1166">
+        <v>14285</v>
+      </c>
+      <c r="E1166">
+        <v>1856</v>
+      </c>
+      <c r="F1166">
+        <v>16690</v>
+      </c>
+      <c r="G1166">
+        <v>3806</v>
+      </c>
+      <c r="H1166">
+        <v>56150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1166"/>
+  <dimension ref="A1:H1167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30712,6 +30712,32 @@
         <v>56150</v>
       </c>
     </row>
+    <row r="1167" spans="1:8">
+      <c r="A1167" s="1">
+        <v>1165</v>
+      </c>
+      <c r="B1167" s="2">
+        <v>46248</v>
+      </c>
+      <c r="C1167">
+        <v>3248</v>
+      </c>
+      <c r="D1167">
+        <v>14545</v>
+      </c>
+      <c r="E1167">
+        <v>1846</v>
+      </c>
+      <c r="F1167">
+        <v>16575</v>
+      </c>
+      <c r="G1167">
+        <v>3875</v>
+      </c>
+      <c r="H1167">
+        <v>56075</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1167"/>
+  <dimension ref="A1:H1168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30738,6 +30738,32 @@
         <v>56075</v>
       </c>
     </row>
+    <row r="1168" spans="1:8">
+      <c r="A1168" s="1">
+        <v>1166</v>
+      </c>
+      <c r="B1168" s="2">
+        <v>46251</v>
+      </c>
+      <c r="C1168">
+        <v>3272</v>
+      </c>
+      <c r="D1168">
+        <v>14850</v>
+      </c>
+      <c r="E1168">
+        <v>1851.5</v>
+      </c>
+      <c r="F1168">
+        <v>16670</v>
+      </c>
+      <c r="G1168">
+        <v>3855</v>
+      </c>
+      <c r="H1168">
+        <v>56225</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1168"/>
+  <dimension ref="A1:H1169"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30764,6 +30764,32 @@
         <v>56225</v>
       </c>
     </row>
+    <row r="1169" spans="1:8">
+      <c r="A1169" s="1">
+        <v>1167</v>
+      </c>
+      <c r="B1169" s="2">
+        <v>46252</v>
+      </c>
+      <c r="C1169">
+        <v>3219</v>
+      </c>
+      <c r="D1169">
+        <v>14335</v>
+      </c>
+      <c r="E1169">
+        <v>1840.5</v>
+      </c>
+      <c r="F1169">
+        <v>16740</v>
+      </c>
+      <c r="G1169">
+        <v>3795</v>
+      </c>
+      <c r="H1169">
+        <v>55550</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1169"/>
+  <dimension ref="A1:H1170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30790,6 +30790,32 @@
         <v>55550</v>
       </c>
     </row>
+    <row r="1170" spans="1:8">
+      <c r="A1170" s="1">
+        <v>1168</v>
+      </c>
+      <c r="B1170" s="2">
+        <v>46253</v>
+      </c>
+      <c r="C1170">
+        <v>3191.5</v>
+      </c>
+      <c r="D1170">
+        <v>14180</v>
+      </c>
+      <c r="E1170">
+        <v>1827</v>
+      </c>
+      <c r="F1170">
+        <v>16690</v>
+      </c>
+      <c r="G1170">
+        <v>3750</v>
+      </c>
+      <c r="H1170">
+        <v>54375</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1170"/>
+  <dimension ref="A1:H1171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30816,6 +30816,32 @@
         <v>54375</v>
       </c>
     </row>
+    <row r="1171" spans="1:8">
+      <c r="A1171" s="1">
+        <v>1169</v>
+      </c>
+      <c r="B1171" s="2">
+        <v>46254</v>
+      </c>
+      <c r="C1171">
+        <v>3182</v>
+      </c>
+      <c r="D1171">
+        <v>14170</v>
+      </c>
+      <c r="E1171">
+        <v>1848</v>
+      </c>
+      <c r="F1171">
+        <v>16660</v>
+      </c>
+      <c r="G1171">
+        <v>3865.5</v>
+      </c>
+      <c r="H1171">
+        <v>54850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1171"/>
+  <dimension ref="A1:H1172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30842,6 +30842,32 @@
         <v>54850</v>
       </c>
     </row>
+    <row r="1172" spans="1:8">
+      <c r="A1172" s="1">
+        <v>1170</v>
+      </c>
+      <c r="B1172" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C1172">
+        <v>3227</v>
+      </c>
+      <c r="D1172">
+        <v>14291</v>
+      </c>
+      <c r="E1172">
+        <v>1857</v>
+      </c>
+      <c r="F1172">
+        <v>16860</v>
+      </c>
+      <c r="G1172">
+        <v>3980</v>
+      </c>
+      <c r="H1172">
+        <v>55900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1172"/>
+  <dimension ref="A1:H1173"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30868,6 +30868,32 @@
         <v>55900</v>
       </c>
     </row>
+    <row r="1173" spans="1:8">
+      <c r="A1173" s="1">
+        <v>1171</v>
+      </c>
+      <c r="B1173" s="2">
+        <v>46258</v>
+      </c>
+      <c r="C1173">
+        <v>3215.5</v>
+      </c>
+      <c r="D1173">
+        <v>14344</v>
+      </c>
+      <c r="E1173">
+        <v>1862.5</v>
+      </c>
+      <c r="F1173">
+        <v>16940</v>
+      </c>
+      <c r="G1173">
+        <v>3985</v>
+      </c>
+      <c r="H1173">
+        <v>55900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1173"/>
+  <dimension ref="A1:H1174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30894,6 +30894,32 @@
         <v>55900</v>
       </c>
     </row>
+    <row r="1174" spans="1:8">
+      <c r="A1174" s="1">
+        <v>1172</v>
+      </c>
+      <c r="B1174" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C1174">
+        <v>3188</v>
+      </c>
+      <c r="D1174">
+        <v>14425</v>
+      </c>
+      <c r="E1174">
+        <v>1867</v>
+      </c>
+      <c r="F1174">
+        <v>16780</v>
+      </c>
+      <c r="G1174">
+        <v>3987</v>
+      </c>
+      <c r="H1174">
+        <v>55700</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1174"/>
+  <dimension ref="A1:H1175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30920,6 +30920,32 @@
         <v>55700</v>
       </c>
     </row>
+    <row r="1175" spans="1:8">
+      <c r="A1175" s="1">
+        <v>1173</v>
+      </c>
+      <c r="B1175" s="2">
+        <v>46260</v>
+      </c>
+      <c r="C1175">
+        <v>3227.5</v>
+      </c>
+      <c r="D1175">
+        <v>14525</v>
+      </c>
+      <c r="E1175">
+        <v>1866</v>
+      </c>
+      <c r="F1175">
+        <v>16895</v>
+      </c>
+      <c r="G1175">
+        <v>4107</v>
+      </c>
+      <c r="H1175">
+        <v>55300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1175"/>
+  <dimension ref="A1:H1176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30946,6 +30946,32 @@
         <v>55300</v>
       </c>
     </row>
+    <row r="1176" spans="1:8">
+      <c r="A1176" s="1">
+        <v>1174</v>
+      </c>
+      <c r="B1176" s="2">
+        <v>46261</v>
+      </c>
+      <c r="C1176">
+        <v>3212.5</v>
+      </c>
+      <c r="D1176">
+        <v>14490</v>
+      </c>
+      <c r="E1176">
+        <v>1872</v>
+      </c>
+      <c r="F1176">
+        <v>16660</v>
+      </c>
+      <c r="G1176">
+        <v>4107</v>
+      </c>
+      <c r="H1176">
+        <v>54950</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1176"/>
+  <dimension ref="A1:H1177"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30972,6 +30972,32 @@
         <v>54950</v>
       </c>
     </row>
+    <row r="1177" spans="1:8">
+      <c r="A1177" s="1">
+        <v>1175</v>
+      </c>
+      <c r="B1177" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C1177">
+        <v>3222</v>
+      </c>
+      <c r="D1177">
+        <v>14535</v>
+      </c>
+      <c r="E1177">
+        <v>1880</v>
+      </c>
+      <c r="F1177">
+        <v>16850</v>
+      </c>
+      <c r="G1177">
+        <v>4070</v>
+      </c>
+      <c r="H1177">
+        <v>55125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LME/parser_beta_2.0/data/LME_db_new.xlsx
+++ b/LME/parser_beta_2.0/data/LME_db_new.xlsx
@@ -396,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1177"/>
+  <dimension ref="A1:H1178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -30998,6 +30998,32 @@
         <v>55125</v>
       </c>
     </row>
+    <row r="1178" spans="1:8">
+      <c r="A1178" s="1">
+        <v>1176</v>
+      </c>
+      <c r="B1178" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C1178">
+        <v>3261</v>
+      </c>
+      <c r="D1178">
+        <v>14395.5</v>
+      </c>
+      <c r="E1178">
+        <v>1874</v>
+      </c>
+      <c r="F1178">
+        <v>16350</v>
+      </c>
+      <c r="G1178">
+        <v>4115</v>
+      </c>
+      <c r="H1178">
+        <v>54725</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
